--- a/02-session/ThesaurusJuly.xlsx
+++ b/02-session/ThesaurusJuly.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/82d0fc462f1d9a6e/Documentos/July/jesusAriel/ADSO-2901817-July-Ramos/02-session/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="9" documentId="13_ncr:1_{0D6C6AF3-C926-4B52-AF3A-BD8A6D7056E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BD5C5979-CFF4-49DD-A609-29D7CD5E4D3B}"/>
+  <xr:revisionPtr revIDLastSave="10" documentId="13_ncr:1_{0D6C6AF3-C926-4B52-AF3A-BD8A6D7056E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A13D4048-E6F1-492A-9BE2-19A4C9A96396}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{CBF535E4-71E5-47C2-9BF5-65E8EF8C5F03}"/>
   </bookViews>
@@ -6421,8 +6421,9 @@
     <hyperlink ref="D16" r:id="rId11" xr:uid="{AF2210DD-1F30-460E-BFFB-B39256E58B9B}"/>
     <hyperlink ref="D19" r:id="rId12" xr:uid="{2B0AD326-AEE5-4918-BD2B-10C359FAFF3B}"/>
     <hyperlink ref="D20" r:id="rId13" xr:uid="{01A8A458-76C3-492D-B5B1-CA0B10D14D40}"/>
+    <hyperlink ref="D17" r:id="rId14" xr:uid="{3AF19899-D03D-43B2-825B-00F24B0A252B}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId14"/>
+  <pageSetup orientation="portrait" r:id="rId15"/>
 </worksheet>
 </file>